--- a/astro-site/public/dl/guia-chocolateria-obrador/campanas-y-valle-del-ano.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/campanas-y-valle-del-ano.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>6 dias por semana x 52 semanas = 312, menos 8 dias de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bomboneria de menos de 300 m2 tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
+          <t>6 días por semana x 52 semanas = 312, menos 8 días de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bombonería de menos de 300 m² tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Grupo 5, «Personal de apoyo», del convenio de la Comunidad de Madrid (código 28001025011981, denominación oficial en REGCON «CONFITERIAS PASTELERIAS Y REPOSTERIA (COMERCIO E INDUSTRIA)»). Es un EJEMPLO: sustitúyelo por el de TU convenio. Y ojo: está PROBADO que no existe un convenio estatal del chocolate.</t>
+          <t>Grupo 5, «Personal de apoyo y ayuda en servicios auxiliares», del convenio de la Comunidad de Madrid (código 28001025011981, denominación oficial en REGCON «CONFITERÍAS PASTELERÍAS Y REPOSTERÍA (COMERCIO E INDUSTRIA)»). Es un EJEMPLO: sustitúyelo por el de TU convenio. Y ojo: está PROBADO que no existe un convenio estatal del chocolate.</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>TF4 - Turron de chocolate con almendra, 250 g</t>
+          <t>TF4 - Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Q7" s="19" t="inlineStr">
         <is>
-          <t>Reyes (6): liquidar turron y figuras de Navidad · rebajas post-Navidad · lanzar la coleccion de invierno · planificar San Valentin</t>
+          <t>Reyes (6): liquidar turrón y figuras de Navidad · rebajas post-Navidad · lanzar la colección de invierno · planificar San Valentín</t>
         </is>
       </c>
       <c r="R7" s="19" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="S7" s="11" t="inlineStr">
         <is>
-          <t>Fecha menor: cierra la produccion de Navidad y liquida el stock. Lo que se produce para Reyes ya esta hecho en diciembre.</t>
+          <t>Fecha menor: cierra la producción de Navidad y liquida el stock. Lo que se produce para Reyes ya esta hecho en diciembre.</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>San Valentin</t>
+          <t>San Valentín</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>San Valentin (14): corazones y edicion limitada · fecha limite de encargos el dia 10 · entregas expres los dias 13 y 14</t>
+          <t>San Valentín (14): corazones y edición limitada · fecha limite de encargos el día 10 · entregas expres los días 13 y 14</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="S8" s="11" t="inlineStr">
         <is>
-          <t>El pico de regalo. `CHS-34` mide que las ventas de chocolates y dulces pueden DUPLICAR el promedio anual en San Valentin, y que hay companias que hacen en ese solo evento hasta el 10 % de su venta anual: ese 10 % es de una compania concreta, no una regla del sector. La fecha limite de encargos la publica el propio kit: el dia 10.</t>
+          <t>El pico de regalo. `CHS-34` mide que las ventas de chocolates y dulces pueden DUPLICAR el promedio anual en San Valentín, y que hay companias que hacen en ese solo evento hasta el 10 % de su venta anual: ese 10 % es de una compania concreta, no una regla del sector. La fecha limite de encargos la publica el propio kit: el día 10.</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Dia del Padre</t>
+          <t>Día del Padre</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Q9" s="19" t="inlineStr">
         <is>
-          <t>Dia del Padre (19) · preparacion de Pascua (fecha movil) · talleres infantiles de Semana Santa</t>
+          <t>Día del Padre (19) · preparación de Pascua (fecha móvil) · talleres infantiles de Semana Santa</t>
         </is>
       </c>
       <c r="R9" s="19" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="S9" s="11" t="inlineStr">
         <is>
-          <t>Fecha menor, y el mes en el que ya hay que estar produciendo Pascua. Los talleres infantiles de Semana Santa son la primera vez del ano en que la sala factura por hora en vez de por bombon.</t>
+          <t>Fecha menor, y el mes en el que ya hay que estar produciendo Pascua. Los talleres infantiles de Semana Santa son la primera vez del año en que la sala factura por hora en vez de por bombón.</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
-          <t>Campana de FIGURA Y MOLDE: la compra de moldes va MUY por delante, y es tesoreria inmovilizada que el libro 6 cuantifica. Fecha movil: si la Pascua cae pronto, marzo se come parte de abril.</t>
+          <t>Campana de FIGURA Y MOLDE: la compra de moldes va MUY por delante, y es tesorería inmovilizada que el libro 6 cuantifica. Fecha móvil: si la Pascua cae pronto, marzo se come parte de abril.</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>COMUNIONES (pico) y Dia de la Madre</t>
+          <t>COMUNIONES (pico) y Día de la Madre</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
-          <t>Dia de la Madre (1.er domingo) · pico de COMUNIONES · edicion regalo premium</t>
+          <t>Día de la Madre (1.er domingo) · pico de COMUNIONES · edición regalo premium</t>
         </is>
       </c>
       <c r="R11" s="19" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
-          <t>El pico de las comuniones, y el mes con mas dias de campana del primer semestre. El packaging personalizado va con MAS antelacion que los moldes: es lo contrario de Pascua.</t>
+          <t>El pico de las comuniones, y el mes con mas días de campana del primer semestre. El packaging personalizado va con MAS antelación que los moldes: es lo contrario de Pascua.</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>COMUNIONES (ultimas)</t>
+          <t>COMUNIONES (últimas)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>Ultimas comuniones · inicio del verano: adaptar catalogo (menos ganache fresca, mas tableta y producto estable)</t>
+          <t>Últimas comuniones · inicio del verano: adaptar catálogo (menos ganache fresca, mas tableta y producto estable)</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
         <is>
-          <t>Tabletas con fruta, bombones en camara</t>
+          <t>Tabletas con fruta, bombones en cámara</t>
         </is>
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
-          <t>El mes de apertura de La Almendra (1 de junio): «Media», con seis meses de rodaje por delante hasta Navidad. Y el mes en el que el catalogo EMPIEZA a cambiar, literal del kit: «menos ganache fresca, mas tableta y producto estable». Aqui arranca tambien la parada de ENVIOS, que es de canal online, no de mostrador.</t>
+          <t>El mes de apertura de La Almendra (1 de junio): «Media», con seis meses de rodaje por delante hasta Navidad. Y el mes en el que el catálogo EMPIEZA a cambiar, literal del kit: «menos ganache fresca, mas tableta y producto estable». Aquí arranca también la parada de ENVÍOS, que es de canal online, no de mostrador.</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2214,17 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>Asuncion (15): festivo nacional, la tienda abre para el turista aunque el obrador pare · mantenimiento profundo · vacaciones escalonadas · cerrar el pedido de coberturas de Navidad</t>
+          <t>Asunción (15): festivo nacional, la tienda abre para el turista aunque el obrador pare · mantenimiento profundo · vacaciones escalonadas · cerrar el pedido de coberturas de Navidad</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>Produccion reducida, planificacion Q4</t>
+          <t>Producción reducida, planificación Q4</t>
         </is>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>EL UNICO MES «BAJA» DE LOS DOCE. Lo que para es el OBRADOR, no la caja: el literal del kit es «la tienda abre para el turista aunque el obrador pare». Y es el mes en el que se CIERRA EL PEDIDO DE COBERTURAS DE NAVIDAD, que es la decision de tesoreria mas grande del ano.</t>
+          <t>EL ÚNICO MES «BAJA» DE LOS DOCE. Lo que para es el OBRADOR, no la caja: el literal del kit es «la tienda abre para el turista aunque el obrador pare». Y es el mes en el que se CIERRA EL PEDIDO DE COBERTURAS DE NAVIDAD, que es la decisión de tesorería mas grande del año.</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Q15" s="19" t="inlineStr">
         <is>
-          <t>Vuelta a la rutina · coleccion de otono · ferias gastronomicas · abrir la agenda de pedidos corporativos de Navidad</t>
+          <t>Vuelta a la rutina · colección de otoño · ferias gastronomicas · abrir la agenda de pedidos corporativos de Navidad</t>
         </is>
       </c>
       <c r="R15" s="19" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="S15" s="11" t="inlineStr">
         <is>
-          <t>El mes que decide diciembre: aqui se abre la agenda corporativa, y el plazo minimo de un pedido de empresa es de 14 dias desde la aprobacion de la muestra (`CHS-55`). Vender un estuche corporativo el 15 de diciembre no es una venta: es una promesa que no se puede cumplir.</t>
+          <t>El mes que decide diciembre: aquí se abre la agenda corporativa, y el plazo mínimo de un pedido de empresa es de 14 días desde la aprobación de la muestra (`CHS-55`). Vender un estuche corporativo el 15 de diciembre no es una venta: es una promesa que no se puede cumplir.</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>Halloween (31): figuras y bombones de temporada · produccion navidena a pleno · publicar el catalogo de Navidad</t>
+          <t>Halloween (31): figuras y bombones de temporada · producción navidena a pleno · publicar el catálogo de Navidad</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="S16" s="11" t="inlineStr">
         <is>
-          <t>Arranque de la temporada alta. Lo importante de octubre NO es Halloween: es que la produccion de Navidad ya va a pleno y se PAGA aqui, para cobrarse en diciembre. Ese desfase es lo que el libro 7 pone en la tesoreria mes a mes.</t>
+          <t>Arranque de la temporada alta. Lo importante de octubre NO es Halloween: es que la producción de Navidad ya va a pleno y se PAGA aquí, para cobrarse en diciembre. Ese desfase es lo que el libro 7 pone en la tesorería mes a mes.</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="Q17" s="19" t="inlineStr">
         <is>
-          <t>Todos los Santos (1): panellets y huesos de santo banados · Black Friday (ultimo viernes) · preventa de Navidad · turrones y cestas</t>
+          <t>Todos los Santos (1): panellets y huesos de santo banados · Black Friday (último viernes) · preventa de Navidad · turrones y cestas</t>
         </is>
       </c>
       <c r="R17" s="19" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="S17" s="11" t="inlineStr">
         <is>
-          <t>Dos campanas en un mes y ninguna se parece: Todos los Santos es produccion de obrador a pieza pequena (los huesos de santo, TF3, la unica referencia con huevo), y Black Friday es canal ONLINE con descuento. Ojo con el descuento: subir en noviembre para «rebajar» en diciembre NO cumple la regla de los 30 dias del art. 20 de la Ley 7/1996 en la redaccion del RDL 24/2021 (`CHN-76`) - que NO es el art. 20 del TRLGDCU.</t>
+          <t>Dos campanas en un mes y ninguna se parece: Todos los Santos es producción de obrador a pieza pequeña (los huesos de santo, TF3, la única referencia con huevo), y Black Friday es canal ONLINE con descuento. Ojo con el descuento: subir en noviembre para «rebajar» en diciembre NO cumple la regla de los 30 días del art. 20 de la Ley 7/1996 en la redacción del RDL 24/2021 (`CHN-76`) - que NO es el art. 20 del TRLGDCU.</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>NAVIDAD, maxima produccion · puente de la Constitucion y la Inmaculada (6-8): fin de semana largo de maxima venta en tienda · fecha limite de encargos y horarios especiales del 24 y el 31</t>
+          <t>NAVIDAD, máxima producción · puente de la Constitución y la Inmaculada (6-8): fin de semana largo de máxima venta en tienda · fecha limite de encargos y horarios especiales del 24 y el 31</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="S18" s="11" t="inlineStr">
         <is>
-          <t>LA CAMPANA MAYOR, y la que decide el ano. Su pedido corporativo se cierra en octubre y su limite de produccion lo calcula el libro 7 HACIA ATRAS desde la capacidad del libro 1 (cruce 7 &lt;- 1 de `CRUCES`). La fecha limite de encargos y los horarios del 24 y el 31 los publica el propio kit.</t>
+          <t>LA CAMPANA MAYOR, y la que decide el año. Su pedido corporativo se cierra en octubre y su limite de producción lo calcula el libro 7 HACIA ATRÁS desde la capacidad del libro 1 (cruce 7 &lt;- 1 de `CRUCES`). La fecha limite de encargos y los horarios del 24 y el 31 los publica el propio kit.</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>San Valentin</t>
+          <t>San Valentín</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Dia del Padre</t>
+          <t>Día del Padre</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3313,7 +3313,7 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>COMUNIONES (pico) y Dia de la Madre</t>
+          <t>COMUNIONES (pico) y Día de la Madre</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3345,7 +3345,7 @@
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>COMUNIONES (ultimas)</t>
+          <t>COMUNIONES (últimas)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>San Valentin</t>
+          <t>San Valentín</t>
         </is>
       </c>
       <c r="C13" s="17">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Dia del Padre</t>
+          <t>Día del Padre</t>
         </is>
       </c>
       <c r="C14" s="17">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>COMUNIONES (pico) y Dia de la Madre</t>
+          <t>COMUNIONES (pico) y Día de la Madre</t>
         </is>
       </c>
       <c r="C16" s="17">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>COMUNIONES (ultimas)</t>
+          <t>COMUNIONES (últimas)</t>
         </is>
       </c>
       <c r="C17" s="17">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>San Valentin</t>
+          <t>San Valentín</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Dia del Padre</t>
+          <t>Día del Padre</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>COMUNIONES (pico) y Dia de la Madre</t>
+          <t>COMUNIONES (pico) y Día de la Madre</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>COMUNIONES (ultimas)</t>
+          <t>COMUNIONES (últimas)</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">

--- a/astro-site/public/dl/guia-chocolateria-obrador/campanas-y-valle-del-ano.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/campanas-y-valle-del-ano.xlsx
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>TF5 - Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>TF5 - Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="R15" s="19" t="inlineStr">
         <is>
-          <t>Bombones de frutos secos, praline, especiados</t>
+          <t>Bombones de frutos secos, praliné, especiados</t>
         </is>
       </c>
       <c r="S15" s="11" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>TF3 - Hueso de santo banado en chocolate</t>
+          <t>TF3 - Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="Q17" s="19" t="inlineStr">
         <is>
-          <t>Todos los Santos (1): panellets y huesos de santo banados · Black Friday (último viernes) · preventa de Navidad · turrones y cestas</t>
+          <t>Todos los Santos (1): panellets y huesos de santo bañados · Black Friday (último viernes) · preventa de Navidad · turrones y cestas</t>
         </is>
       </c>
       <c r="R17" s="19" t="inlineStr">
         <is>
-          <t>Panellets y huesos de santo banados, turrones, cestas corporativas, figuras navidenas</t>
+          <t>Panellets y huesos de santo bañados, turrones, cestas corporativas, figuras navidenas</t>
         </is>
       </c>
       <c r="S17" s="11" t="inlineStr">
